--- a/artfynd/S 3898-2024 artfynd.xlsx
+++ b/artfynd/S 3898-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY116"/>
+  <dimension ref="A1:AZ116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125629781</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125652652</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,6 +1037,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125043731</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1143,6 +1163,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129577398</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1270,6 +1295,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125652004</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1367,6 +1397,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75754504</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1464,6 +1499,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75754506</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1561,6 +1601,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75754474</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1658,6 +1703,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75754473</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1765,6 +1815,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125041132</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1872,6 +1927,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125041155</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1979,6 +2039,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125043275</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2086,6 +2151,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125043351</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2193,6 +2263,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125043458</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2300,6 +2375,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125043561</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2426,6 +2506,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125041471</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2552,6 +2637,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125041528</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2673,6 +2763,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125654821</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2799,6 +2894,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125041240</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2906,6 +3006,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125041684</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3013,6 +3118,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125041282</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3120,6 +3230,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125684244</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3227,6 +3342,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125684576</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3334,6 +3454,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125684994</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3441,6 +3566,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125682195</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3548,6 +3678,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125683158</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3655,6 +3790,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125683520</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3762,6 +3902,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125683014</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3883,6 +4028,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125681747</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3986,6 +4136,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125572514</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4107,6 +4262,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130021427</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4213,6 +4373,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72870981</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4314,6 +4479,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121430838</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4416,6 +4586,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123925358</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4517,6 +4692,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123925346</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4624,6 +4804,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124028545</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4725,6 +4910,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123925384</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4832,6 +5022,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123992659</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4939,6 +5134,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124024050</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5046,6 +5246,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124026779</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5153,6 +5358,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124029112</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5260,6 +5470,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124029906</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5367,6 +5582,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124088071</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5474,6 +5694,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124097772</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5581,6 +5806,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124097862</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5682,6 +5912,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128205134</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5783,6 +6018,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128205138</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5890,6 +6130,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128338411</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5997,6 +6242,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132351979</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6123,6 +6373,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124088113</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6249,6 +6504,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123992413</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6371,6 +6631,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123992559</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6497,6 +6762,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123992587</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6623,6 +6893,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123992684</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6745,6 +7020,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123992718</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6871,6 +7151,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123992790</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6997,6 +7282,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124023351</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7123,6 +7413,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124023435</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7249,6 +7544,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124023524</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7375,6 +7675,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124023810</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7501,6 +7806,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124023906</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7623,6 +7933,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124023964</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7749,6 +8064,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124024007</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7875,6 +8195,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124024261</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8001,6 +8326,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124025561</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8127,6 +8457,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124025985</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8253,6 +8588,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124026018</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8379,6 +8719,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124026072</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8510,6 +8855,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124026181</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8636,6 +8986,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124026622</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8757,6 +9112,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124026882</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8883,6 +9243,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124026953</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -9009,6 +9374,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124026992</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9140,6 +9510,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124027283</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9266,6 +9641,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124027544</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9392,6 +9772,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124027666</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9518,6 +9903,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124027716</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9644,6 +10034,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124027790</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9770,6 +10165,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124027886</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9896,6 +10296,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124027935</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -10022,6 +10427,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124028440</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -10148,6 +10558,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124028562</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10274,6 +10689,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124028591</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10400,6 +10820,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124028798</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10526,6 +10951,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124028866</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10652,6 +11082,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124029362</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10783,6 +11218,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124029428</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10909,6 +11349,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124029506</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -11035,6 +11480,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124086771</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -11161,6 +11611,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124086828</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -11287,6 +11742,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124086926</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11413,6 +11873,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124087205</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11539,6 +12004,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124087279</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11665,6 +12135,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124087313</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11791,6 +12266,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124087342</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11917,6 +12397,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124087343</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -12048,6 +12533,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124087360</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -12174,6 +12664,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124087560</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -12300,6 +12795,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124088099</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12426,6 +12926,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124088146</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12547,6 +13052,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127351239</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12671,6 +13181,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121753465</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12797,6 +13312,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127350784</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12928,6 +13448,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127351593</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -13049,6 +13574,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127352049</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -13160,6 +13690,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127353389</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -13284,6 +13819,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119151080</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -13390,6 +13930,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134232481</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13491,6 +14036,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121396945</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13592,6 +14142,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128205420</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13694,6 +14249,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130339924</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13801,6 +14361,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128468992</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13908,6 +14473,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128468956</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -14023,6 +14593,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122988077</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -14124,8 +14699,130 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128205413</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>